--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -73,16 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
     <t>ATLAHUA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>BAUTISTA</t>
@@ -94,6 +97,9 @@
     <t>CANTE</t>
   </si>
   <si>
+    <t>CONDE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -106,24 +112,24 @@
     <t>PARRA</t>
   </si>
   <si>
-    <t>PUGA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>ESTRADA</t>
   </si>
   <si>
@@ -136,37 +142,31 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
     <t>CARBAJAL</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>GERMAN</t>
   </si>
   <si>
-    <t>ALDO</t>
-  </si>
-  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>MIRIAM AIMAR</t>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
   <si>
     <t>VANNYA</t>
@@ -184,6 +184,9 @@
     <t>TOMAS RAFAEL</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>PABLO</t>
   </si>
   <si>
@@ -197,12 +200,6 @@
   </si>
   <si>
     <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
   </si>
 </sst>
 </file>
@@ -603,16 +600,16 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>78.05</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H2">
         <v>7.2</v>
@@ -626,7 +623,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -635,10 +632,10 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -720,16 +717,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.73</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,19 +740,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,16 +769,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>47.22</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -828,10 +834,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>32</v>
@@ -840,7 +846,7 @@
         <v>78.05</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -851,22 +857,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
         <v>7</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>33</v>
       </c>
       <c r="G3">
-        <v>80.48999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -883,16 +889,16 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>63.89</v>
+        <v>58.33</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +940,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920261</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -943,13 +949,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -957,7 +963,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920272</v>
+        <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -966,7 +972,7 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -989,7 +995,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1003,16 +1009,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920370</v>
+        <v>22330051920312</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1026,39 +1032,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920232</v>
+        <v>22330051920315</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920243</v>
+        <v>22330051920232</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1072,22 +1078,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>22330051920243</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1095,22 +1101,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920290</v>
+        <v>22330051920405</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1118,16 +1124,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920293</v>
+        <v>22330051920290</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1141,16 +1147,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920297</v>
+        <v>22330051920293</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1164,16 +1170,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920307</v>
+        <v>22330051920360</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1187,16 +1193,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920419</v>
+        <v>22330051920297</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1210,16 +1216,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920309</v>
+        <v>22330051920307</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1233,16 +1239,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920311</v>
+        <v>22330051920419</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1256,7 +1262,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920312</v>
+        <v>22330051920309</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
@@ -1265,7 +1271,7 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1279,16 +1285,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920315</v>
+        <v>22330051920311</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>ATLAHUA</t>
   </si>
   <si>
@@ -115,46 +112,43 @@
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
     <t>FLORES</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>GERMAN</t>
@@ -908,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -940,22 +934,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920261</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -963,22 +957,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920261</v>
+        <v>22330051920303</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -986,16 +980,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920312</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1009,16 +1003,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920312</v>
+        <v>22330051920315</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1032,39 +1026,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920315</v>
+        <v>22330051920232</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920232</v>
+        <v>22330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1078,22 +1072,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920243</v>
+        <v>22330051920405</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1101,22 +1095,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>22330051920290</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1124,16 +1118,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920290</v>
+        <v>22330051920293</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1147,16 +1141,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920293</v>
+        <v>22330051920360</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1170,16 +1164,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920360</v>
+        <v>22330051920297</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1193,16 +1187,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920297</v>
+        <v>22330051920307</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1216,16 +1210,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B14" t="s">
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1239,16 +1233,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920419</v>
+        <v>22330051920309</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1262,16 +1256,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1280,26 +1271,6 @@
         <v>11</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920311</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ATLAHUA</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -85,9 +91,6 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>AYALA</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -112,9 +118,15 @@
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -142,6 +154,9 @@
     <t>CARBAJAL</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
@@ -151,9 +166,15 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
     <t>GERMAN</t>
   </si>
   <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
@@ -182,6 +203,9 @@
   </si>
   <si>
     <t>PABLO</t>
+  </si>
+  <si>
+    <t>ISAI</t>
   </si>
   <si>
     <t>JOSUE ISRAEL</t>
@@ -711,16 +735,16 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>70.73</v>
+        <v>75.61</v>
       </c>
       <c r="H2">
         <v>7.2</v>
@@ -737,16 +761,16 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -763,19 +787,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>47.22</v>
+        <v>52.78</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -831,16 +855,16 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>78.05</v>
+        <v>75.61</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -883,16 +907,16 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>58.33</v>
+        <v>52.78</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,22 +958,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920261</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -957,22 +981,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920303</v>
+        <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -980,16 +1004,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920312</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1003,16 +1027,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920315</v>
+        <v>22330051920303</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1026,68 +1050,68 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920232</v>
+        <v>22330051920312</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920243</v>
+        <v>22330051920315</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>22330051920232</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1095,22 +1119,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920290</v>
+        <v>22330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1118,22 +1142,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920293</v>
+        <v>22330051920405</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1141,16 +1165,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920360</v>
+        <v>22330051920290</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1164,16 +1188,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920297</v>
+        <v>22330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1187,16 +1211,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920307</v>
+        <v>22330051920360</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1210,16 +1234,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920419</v>
+        <v>22330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1233,16 +1257,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920309</v>
+        <v>22330051920300</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1256,21 +1280,90 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>22330051920307</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920419</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920309</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>22330051920311</v>
       </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>ATLAHUA</t>
   </si>
   <si>
@@ -85,6 +82,12 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
     <t>QUESADA</t>
   </si>
   <si>
@@ -106,21 +109,12 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
     <t>PARRA</t>
   </si>
   <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
@@ -130,6 +124,12 @@
     <t>CORTES</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>OLGUIN</t>
   </si>
   <si>
@@ -157,18 +157,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
     <t>GERMAN</t>
   </si>
   <si>
@@ -178,6 +169,12 @@
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
@@ -206,12 +203,6 @@
   </si>
   <si>
     <t>ISAI</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>MOISES ALBERTO</t>
@@ -926,7 +917,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,22 +949,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>22330051920261</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -981,22 +972,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920261</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1004,16 +995,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920291</v>
+        <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1027,16 +1018,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920303</v>
+        <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1050,16 +1041,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920419</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1073,16 +1064,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920315</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1096,39 +1087,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920232</v>
+        <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920243</v>
+        <v>22330051920232</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1142,22 +1133,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920405</v>
+        <v>22330051920243</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1165,22 +1156,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920290</v>
+        <v>22330051920405</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1188,16 +1179,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920293</v>
+        <v>22330051920290</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1211,16 +1202,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920360</v>
+        <v>22330051920293</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1234,16 +1225,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920297</v>
+        <v>22330051920360</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1257,16 +1248,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920300</v>
+        <v>22330051920297</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1280,16 +1271,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920307</v>
+        <v>22330051920300</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1303,16 +1294,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920419</v>
+        <v>22330051920309</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1326,16 +1317,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1344,26 +1332,6 @@
         <v>11</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920311</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
     <t>PUGA CABRERA</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
   </si>
   <si>
     <t>FLORES</t>
-  </si>
-  <si>
-    <t>GERMAN</t>
   </si>
   <si>
     <t>EFRAIN DE JESUS</t>
@@ -917,7 +908,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,22 +940,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920261</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -972,16 +963,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920303</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -995,16 +986,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920307</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1018,16 +1009,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1041,16 +1032,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920419</v>
+        <v>22330051920312</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1064,16 +1055,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920312</v>
+        <v>22330051920315</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1087,39 +1078,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920232</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920232</v>
+        <v>22330051920243</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1133,22 +1124,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920243</v>
+        <v>22330051920405</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1156,22 +1147,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920405</v>
+        <v>22330051920290</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1179,16 +1170,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920290</v>
+        <v>22330051920293</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1202,16 +1193,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920293</v>
+        <v>22330051920360</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1225,16 +1216,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920360</v>
+        <v>22330051920297</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1248,16 +1239,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920297</v>
+        <v>22330051920300</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1271,16 +1262,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920300</v>
+        <v>22330051920309</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1294,16 +1285,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
-        <v>46</v>
-      </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1312,26 +1300,6 @@
         <v>11</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920311</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -85,18 +85,12 @@
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>AYALA</t>
   </si>
   <si>
-    <t>CANTE</t>
-  </si>
-  <si>
     <t>CONDE</t>
   </si>
   <si>
@@ -112,6 +106,9 @@
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
     <t>LEON</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>VALDEZ</t>
   </si>
   <si>
@@ -154,6 +145,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>MIA</t>
+  </si>
+  <si>
     <t>EFRAIN DE JESUS</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
     <t>DIEGO</t>
   </si>
   <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
     <t>ZABDIEL</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
   </si>
   <si>
     <t>MARCOS</t>
-  </si>
-  <si>
-    <t>TOMAS RAFAEL</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -600,10 +588,10 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -612,7 +600,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -626,10 +614,10 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -638,7 +626,7 @@
         <v>80</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,10 +640,10 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>13</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>23</v>
@@ -664,7 +652,7 @@
         <v>63.89</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -717,19 +705,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,10 +731,10 @@
         <v>40</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -755,7 +743,7 @@
         <v>82.5</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -769,19 +757,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -834,19 +822,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -860,10 +848,10 @@
         <v>40</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>7</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -872,7 +860,7 @@
         <v>82.5</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -886,19 +874,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -908,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -940,22 +928,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920263</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -963,16 +951,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920303</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -986,16 +974,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920307</v>
+        <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1009,16 +997,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920419</v>
+        <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1032,16 +1020,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920419</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1058,13 +1046,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1084,10 +1072,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1107,10 +1095,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1133,7 +1121,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1150,13 +1138,13 @@
         <v>22330051920290</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1170,16 +1158,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920293</v>
+        <v>22330051920360</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1193,16 +1181,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920360</v>
+        <v>22330051920297</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1216,16 +1204,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920297</v>
+        <v>22330051920300</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1239,16 +1227,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920300</v>
+        <v>22330051920309</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1262,16 +1250,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1280,26 +1265,6 @@
         <v>11</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920311</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -97,12 +97,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
@@ -139,12 +133,6 @@
     <t>CARBAJAL</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
@@ -179,12 +167,6 @@
   </si>
   <si>
     <t>PABLO</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>MOISES ALBERTO</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -760,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
         <v>6.2</v>
@@ -877,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,10 +916,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -957,10 +939,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -980,10 +962,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1003,10 +985,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1026,10 +1008,10 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1049,10 +1031,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1072,10 +1054,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1095,10 +1077,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1121,7 +1103,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1141,10 +1123,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1164,10 +1146,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1187,10 +1169,10 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1204,16 +1186,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920300</v>
+        <v>22330051920311</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1222,49 +1201,6 @@
         <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920309</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920311</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -76,18 +76,18 @@
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>AYALA</t>
   </si>
   <si>
@@ -106,67 +106,67 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
     <t>MIA</t>
   </si>
   <si>
     <t>EFRAIN DE JESUS</t>
   </si>
   <si>
+    <t>JOSUE ISRAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JOSUE ISRAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>PABLO</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -956,7 +956,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920307</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -979,7 +979,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920419</v>
+        <v>22330051920315</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920315</v>
+        <v>22330051920232</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -1040,18 +1040,18 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920232</v>
+        <v>22330051920243</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
@@ -1071,13 +1071,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920243</v>
+        <v>22330051920405</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -1086,7 +1086,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1094,13 +1094,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920405</v>
+        <v>22330051920290</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -1109,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920290</v>
+        <v>22330051920360</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920360</v>
+        <v>22330051920297</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920297</v>
+        <v>22330051920303</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -73,58 +73,70 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>CARBAJAL</t>
@@ -133,10 +145,22 @@
     <t>CORTES</t>
   </si>
   <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>EFRAIN DE JESUS</t>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
   </si>
   <si>
     <t>JOSUE ISRAEL</t>
@@ -145,22 +169,16 @@
     <t>DIEGO</t>
   </si>
   <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
     <t>VANNYA</t>
   </si>
   <si>
-    <t>MARIA ANGELES</t>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>PABLO</t>
@@ -807,16 +825,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>78.05</v>
+        <v>70.73</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -833,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -859,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -878,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,22 +928,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920263</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -933,22 +951,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920242</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -956,22 +974,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920307</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -979,22 +997,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920419</v>
+        <v>22330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1002,22 +1020,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920315</v>
+        <v>22330051920402</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1025,91 +1043,91 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920232</v>
+        <v>22330051920403</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920243</v>
+        <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>22330051920419</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920290</v>
+        <v>22330051920232</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1117,22 +1135,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920360</v>
+        <v>22330051920237</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1140,22 +1158,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920297</v>
+        <v>22330051920400</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1163,22 +1181,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920303</v>
+        <v>22330051920405</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1186,13 +1204,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920311</v>
+        <v>22330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1201,6 +1222,49 @@
         <v>11</v>
       </c>
       <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920303</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920311</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>DECTOR</t>
   </si>
   <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>LUNA</t>
@@ -97,94 +118,103 @@
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>FIERROS</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>CORTES</t>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
   </si>
   <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
     <t>JOCELYN</t>
   </si>
   <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
     <t>AILYN</t>
   </si>
   <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN YAEL</t>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
   </si>
   <si>
     <t>JOSUE ISRAEL</t>
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -896,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,16 +958,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,22 +981,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920242</v>
+        <v>22330051920402</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -974,22 +1004,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920403</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -997,16 +1027,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920263</v>
+        <v>22330051920281</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1020,16 +1050,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920395</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1043,22 +1073,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920403</v>
+        <v>22330051920370</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1066,62 +1096,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920307</v>
+        <v>22330051920232</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920419</v>
+        <v>22330051920236</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920232</v>
+        <v>22330051920237</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1135,16 +1165,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920237</v>
+        <v>22330051920242</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1161,13 +1191,13 @@
         <v>22330051920400</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1181,22 +1211,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920405</v>
+        <v>22330051920366</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1204,22 +1234,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920297</v>
+        <v>22330051920263</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1227,22 +1257,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920303</v>
+        <v>22330051920405</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1250,13 +1280,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920311</v>
+        <v>22330051920297</v>
       </c>
       <c r="B16" t="s">
         <v>30</v>
       </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1265,6 +1298,95 @@
         <v>11</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920303</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920307</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920419</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920311</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
+++ b/docentes/Medina Tolentino Francisco - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -73,6 +73,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>PUGA CABRERA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -133,6 +142,9 @@
     <t>GALINDO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ESTRADA</t>
   </si>
   <si>
@@ -163,6 +175,9 @@
     <t>MAYAHUA</t>
   </si>
   <si>
+    <t>KARLOS ARATH</t>
+  </si>
+  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
@@ -176,6 +191,9 @@
   </si>
   <si>
     <t>BRANDON</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
   </si>
   <si>
     <t>MIRIAM AIMAR</t>
@@ -926,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,16 +976,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920369</v>
+        <v>22330051920422</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,22 +999,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920402</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1004,16 +1022,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920403</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1027,16 +1045,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920281</v>
+        <v>22330051920403</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1050,16 +1068,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920395</v>
+        <v>22330051920281</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1073,22 +1091,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920370</v>
+        <v>22330051920395</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1096,62 +1114,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920232</v>
+        <v>22330051920417</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920236</v>
+        <v>22330051920370</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920237</v>
+        <v>22330051920232</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1165,16 +1183,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920242</v>
+        <v>22330051920236</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1188,16 +1206,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920400</v>
+        <v>22330051920237</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1211,16 +1229,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1234,22 +1252,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920263</v>
+        <v>22330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1257,22 +1275,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920405</v>
+        <v>22330051920366</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1280,22 +1298,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920297</v>
+        <v>22330051920263</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1303,22 +1321,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920303</v>
+        <v>22330051920405</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1326,16 +1344,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920307</v>
+        <v>22330051920297</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1349,16 +1367,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920419</v>
+        <v>22330051920303</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1372,13 +1390,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920311</v>
+        <v>22330051920307</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1387,6 +1408,49 @@
         <v>11</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920419</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920311</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>
